--- a/Horarios/Colectivos/136-Rapido/LaboralNavarro.xlsx
+++ b/Horarios/Colectivos/136-Rapido/LaboralNavarro.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>739_43371-1</t>
+          <t>739_43360-1</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -529,7 +529,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>739_43372-1</t>
+          <t>739_43361-1</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -553,7 +553,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>739_43373-1</t>
+          <t>739_43362-1</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -577,7 +577,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>739_43374-1</t>
+          <t>739_43363-1</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>739_43375-1</t>
+          <t>739_43364-1</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -625,7 +625,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>739_43376-1</t>
+          <t>739_43365-1</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>739_43377-1</t>
+          <t>739_43366-1</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -673,7 +673,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>739_43378-1</t>
+          <t>739_43367-1</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -697,7 +697,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>739_43379-1</t>
+          <t>739_43368-1</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>739_43380-1</t>
+          <t>739_43369-1</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -745,7 +745,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>739_43381-1</t>
+          <t>739_43370-1</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -769,7 +769,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>739_43382-1</t>
+          <t>739_43371-1</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>739_43383-1</t>
+          <t>739_43372-1</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -815,7 +815,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>739_43384-1</t>
+          <t>739_43373-1</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>739_43385-1</t>
+          <t>739_43374-1</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>739_43386-1</t>
+          <t>739_43375-1</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -879,11 +879,11 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>739_43387-1</t>
+          <t>739_43376-1</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>739_43388-1</t>
+          <t>739_43377-1</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -931,7 +931,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>739_43389-1</t>
+          <t>739_43378-1</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -957,7 +957,7 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>739_43390-1</t>
+          <t>739_43379-1</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
